--- a/feedback_surveys/034_termination_process_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/034_termination_process_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'redundancy'}</t>
+          <t>redundancy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Redundancy'}</t>
+          <t>Redundancy</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'career_development_opportunities'}</t>
+          <t>career_development_opportunities</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Career Development Opportunities'}</t>
+          <t>Career Development Opportunities</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'career_change'}</t>
+          <t>career_change</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Career Change'}</t>
+          <t>Career Change</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'less_than_1_week'}</t>
+          <t>less_than_1_week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Less than 1 week'}</t>
+          <t>Less than 1 week</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'1_week_-_2_weeks'}</t>
+          <t>1_week_-_2_weeks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': '1 week - 2 weeks'}</t>
+          <t>1 week - 2 weeks</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'2_-_6_weeks'}</t>
+          <t>2_-_6_weeks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': '2 - 6 weeks'}</t>
+          <t>2 - 6 weeks</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'more_than_6_weeks'}</t>
+          <t>more_than_6_weeks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'More than 6 weeks'}</t>
+          <t>More than 6 weeks</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'voluntary'}</t>
+          <t>voluntary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Voluntary'}</t>
+          <t>Voluntary</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'involuntary'}</t>
+          <t>involuntary</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Involuntary'}</t>
+          <t>Involuntary</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'manager_1'}</t>
+          <t>manager_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Manager 1'}</t>
+          <t>Manager 1</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'manager_2'}</t>
+          <t>manager_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Manager 2'}</t>
+          <t>Manager 2</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'manager_3'}</t>
+          <t>manager_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Manager 3'}</t>
+          <t>Manager 3</t>
         </is>
       </c>
     </row>
